--- a/etl/data/inputs/Dr Verweys Tank Cleaning Guide Oil - cleaning and compatibility.xlsx
+++ b/etl/data/inputs/Dr Verweys Tank Cleaning Guide Oil - cleaning and compatibility.xlsx
@@ -224,7 +224,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:T1000"/>
-  <sheetFormatPr defaultColWidth="12.640625" defaultRowHeight="15.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="12.66015625" defaultRowHeight="15.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
@@ -1288,7 +1288,7 @@
         <v>22</v>
       </c>
       <c r="E34" s="3" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="F34" s="2"/>
       <c r="G34" s="2"/>
@@ -1320,7 +1320,7 @@
         <v>22</v>
       </c>
       <c r="E35" s="3" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="F35" s="2"/>
       <c r="G35" s="2"/>
@@ -1352,7 +1352,7 @@
         <v>22</v>
       </c>
       <c r="E36" s="3" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="F36" s="2"/>
       <c r="G36" s="2"/>
@@ -1384,7 +1384,7 @@
         <v>22</v>
       </c>
       <c r="E37" s="3" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="F37" s="2"/>
       <c r="G37" s="2"/>
@@ -1446,7 +1446,7 @@
         <v>22</v>
       </c>
       <c r="E39" s="3" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="F39" s="2"/>
       <c r="G39" s="2"/>
@@ -1478,7 +1478,7 @@
         <v>22</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="F40" s="2"/>
       <c r="G40" s="2"/>
@@ -1510,7 +1510,7 @@
         <v>22</v>
       </c>
       <c r="E41" s="3" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="F41" s="2"/>
       <c r="G41" s="2"/>
